--- a/luaran/templates/tables/Table6_MD2019_Classification.xlsx
+++ b/luaran/templates/tables/Table6_MD2019_Classification.xlsx
@@ -461,19 +461,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,64 +490,71 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Training
+Time (min)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ring (n=170)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Schizont (n=286)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Trophozoite (n=127)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -561,28 +569,31 @@
       <c r="B3" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>0.8645</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>0.8412999999999999</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>0.8571</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>0.8864</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>0.9317</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>0.9184</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="J3" s="6" t="n">
         <v>0.7236</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>0.712</v>
       </c>
     </row>
@@ -595,28 +606,31 @@
       <c r="B4" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>0.8525</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>0.8320000000000001</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>0.8556</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>0.8964</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="6" t="n">
         <v>0.9228</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>0.8996</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>0.6935</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>0.6853</v>
       </c>
     </row>
@@ -629,28 +643,31 @@
       <c r="B5" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>0.8491</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>0.8188</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>0.8875999999999999</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.885</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>0.8938</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>0.9031</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>0.6885</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>0.6747</v>
       </c>
     </row>
@@ -663,28 +680,31 @@
       <c r="B6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>0.8456</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>0.8370000000000001</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>0.8686</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.8812</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>0.9421</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="6" t="n">
         <v>0.8954</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>0.651</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>0.7029</v>
       </c>
     </row>
@@ -697,28 +717,31 @@
       <c r="B7" s="5" t="n">
         <v>25.6</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>0.8439</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="E7" s="6" t="n">
         <v>0.8245999999999999</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>0.8449</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>0.8852</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="6" t="n">
         <v>0.9151</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>0.8905</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.6825</v>
       </c>
     </row>
@@ -731,39 +754,43 @@
       <c r="B8" s="5" t="n">
         <v>44.5</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>0.8421999999999999</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>0.8136</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>0.8547</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>0.8768</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="6" t="n">
         <v>0.9078000000000001</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.9014</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>0.6721</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.6586</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
+  <mergeCells count="8">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luaran/templates/tables/Table6_MD2019_Classification.xlsx
+++ b/luaran/templates/tables/Table6_MD2019_Classification.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MD_2019 Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MD_2019 Stages" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
